--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-04-2026.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>£13.0</t>
+          <t>£13.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£15.9</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>£18.4</t>
+          <t>£19.65</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£20.85</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£25.8</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£29.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>£28.44</t>
+          <t>£29.08</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£33.12</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£36.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>£33.89</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>£39.6</t>
+          <t>£42.4</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>£41.0</t>
+          <t>£43.3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>£47.5</t>
+          <t>£52.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>£49.42</t>
+          <t>£52.8</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>£52.0</t>
+          <t>£53.35</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>£934.92</t>
+          <t>£1020.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£37.77</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£50.5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>£51.8</t>
+          <t>£58.91</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>£54.65</t>
+          <t>£62.37</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>£58.97</t>
+          <t>£66.96</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2741,19 +2741,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>£49.82</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>£49.82</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>£49.82</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>£63.25</t>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>£53.95</t>
+          <t>£61.63</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>£1378.56</t>
+          <t>£1579.36</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>£1540.32</t>
+          <t>£1762.4</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>£1467.52</t>
+          <t>£1677.76</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
